--- a/planned.xlsx
+++ b/planned.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uzk-my.sharepoint.com/personal/linus_palm_uzk_onmicrosoft_com/Documents/Master/MA/master-thesis-nurse-scheduling/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="443" documentId="13_ncr:1_{572483D8-A287-5545-9F3E-BD84B65E9158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C460C037-3834-314E-A275-08C1084351E4}"/>
+  <xr:revisionPtr revIDLastSave="663" documentId="13_ncr:1_{572483D8-A287-5545-9F3E-BD84B65E9158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7770243-FD69-D34D-860F-756D6C3987B5}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dienstplan" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="23">
   <si>
     <t>Name</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>N18</t>
+  </si>
+  <si>
+    <t>Z</t>
+  </si>
+  <si>
+    <t>U</t>
   </si>
 </sst>
 </file>
@@ -522,13 +528,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG21"/>
+  <dimension ref="A1:AF21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -622,53 +628,69 @@
       <c r="AE1" s="2">
         <v>29</v>
       </c>
-      <c r="AF1" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="I2" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
+      <c r="K2" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
+      <c r="P2" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
+      <c r="R2" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
       <c r="V2" s="4"/>
-      <c r="W2" s="4"/>
+      <c r="W2" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="X2" s="4"/>
-      <c r="Y2" s="4"/>
+      <c r="Y2" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="Z2" s="4"/>
       <c r="AA2" s="4"/>
       <c r="AB2" s="4"/>
       <c r="AC2" s="4"/>
-      <c r="AD2" s="4"/>
+      <c r="AD2" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="AE2" s="4"/>
-      <c r="AF2" s="4"/>
-    </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="D3" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -680,7 +702,9 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
+      <c r="P3" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
       <c r="S3" s="4"/>
@@ -694,11 +718,12 @@
       <c r="AA3" s="4"/>
       <c r="AB3" s="4"/>
       <c r="AC3" s="4"/>
-      <c r="AD3" s="4"/>
+      <c r="AD3" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="AE3" s="4"/>
-      <c r="AF3" s="4"/>
-    </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -716,25 +741,52 @@
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4"/>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
+      <c r="P4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC4" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="AD4" s="4"/>
       <c r="AE4" s="4"/>
-      <c r="AF4" s="4"/>
-    </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>4</v>
       </c>
@@ -768,9 +820,8 @@
       <c r="AC5" s="4"/>
       <c r="AD5" s="4"/>
       <c r="AE5" s="4"/>
-      <c r="AF5" s="4"/>
-    </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>5</v>
       </c>
@@ -795,18 +846,27 @@
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
-      <c r="W6" s="4"/>
-      <c r="X6" s="4"/>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
+      <c r="W6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="X6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA6" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="AB6" s="4"/>
       <c r="AC6" s="4"/>
       <c r="AD6" s="4"/>
       <c r="AE6" s="4"/>
-      <c r="AF6" s="4"/>
-    </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -838,11 +898,14 @@
       <c r="AA7" s="4"/>
       <c r="AB7" s="4"/>
       <c r="AC7" s="4"/>
-      <c r="AD7" s="4"/>
-      <c r="AE7" s="4"/>
-      <c r="AF7" s="4"/>
-    </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AD7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE7" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>7</v>
       </c>
@@ -876,9 +939,8 @@
       <c r="AC8" s="4"/>
       <c r="AD8" s="4"/>
       <c r="AE8" s="4"/>
-      <c r="AF8" s="4"/>
-    </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
@@ -896,11 +958,21 @@
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
+      <c r="P9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
@@ -912,9 +984,8 @@
       <c r="AC9" s="4"/>
       <c r="AD9" s="4"/>
       <c r="AE9" s="4"/>
-      <c r="AF9" s="4"/>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
@@ -948,9 +1019,8 @@
       <c r="AC10" s="4"/>
       <c r="AD10" s="4"/>
       <c r="AE10" s="4"/>
-      <c r="AF10" s="4"/>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
@@ -961,13 +1031,27 @@
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
+      <c r="I11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
@@ -982,21 +1066,38 @@
       <c r="AA11" s="4"/>
       <c r="AB11" s="4"/>
       <c r="AC11" s="4"/>
-      <c r="AD11" s="4"/>
-      <c r="AE11" s="4"/>
-      <c r="AF11" s="4"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AD11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE11" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="B12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
@@ -1020,17 +1121,26 @@
       <c r="AC12" s="4"/>
       <c r="AD12" s="4"/>
       <c r="AE12" s="4"/>
-      <c r="AF12" s="4"/>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="B13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -1056,10 +1166,9 @@
       <c r="AC13" s="4"/>
       <c r="AD13" s="4"/>
       <c r="AE13" s="4"/>
-      <c r="AF13" s="4"/>
-      <c r="AG13" s="3"/>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3"/>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>13</v>
       </c>
@@ -1093,9 +1202,8 @@
       <c r="AC14" s="4"/>
       <c r="AD14" s="4"/>
       <c r="AE14" s="4"/>
-      <c r="AF14" s="4"/>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>14</v>
       </c>
@@ -1106,8 +1214,12 @@
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
+      <c r="I15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
@@ -1129,9 +1241,8 @@
       <c r="AC15" s="4"/>
       <c r="AD15" s="4"/>
       <c r="AE15" s="4"/>
-      <c r="AF15" s="4"/>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>15</v>
       </c>
@@ -1142,8 +1253,12 @@
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
+      <c r="I16" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>21</v>
+      </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
@@ -1165,9 +1280,8 @@
       <c r="AC16" s="4"/>
       <c r="AD16" s="4"/>
       <c r="AE16" s="4"/>
-      <c r="AF16" s="4"/>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>16</v>
       </c>
@@ -1178,20 +1292,48 @@
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
       <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
-      <c r="V17" s="4"/>
+      <c r="I17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="O17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="P17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="R17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="S17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="T17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="U17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="V17" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="W17" s="4"/>
       <c r="X17" s="4"/>
       <c r="Y17" s="4"/>
@@ -1201,9 +1343,8 @@
       <c r="AC17" s="4"/>
       <c r="AD17" s="4"/>
       <c r="AE17" s="4"/>
-      <c r="AF17" s="4"/>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>17</v>
       </c>
@@ -1237,9 +1378,8 @@
       <c r="AC18" s="4"/>
       <c r="AD18" s="4"/>
       <c r="AE18" s="4"/>
-      <c r="AF18" s="4"/>
-    </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>18</v>
       </c>
@@ -1273,19 +1413,32 @@
       <c r="AC19" s="4"/>
       <c r="AD19" s="4"/>
       <c r="AE19" s="4"/>
-      <c r="AF19" s="4"/>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="B20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
@@ -1309,9 +1462,8 @@
       <c r="AC20" s="4"/>
       <c r="AD20" s="4"/>
       <c r="AE20" s="4"/>
-      <c r="AF20" s="4"/>
-    </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>20</v>
       </c>
@@ -1336,27 +1488,40 @@
       <c r="T21" s="4"/>
       <c r="U21" s="4"/>
       <c r="V21" s="4"/>
-      <c r="W21" s="4"/>
-      <c r="X21" s="4"/>
-      <c r="Y21" s="4"/>
-      <c r="Z21" s="4"/>
-      <c r="AA21" s="4"/>
-      <c r="AB21" s="4"/>
-      <c r="AC21" s="4"/>
+      <c r="W21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="X21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Z21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB21" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AC21" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="AD21" s="4"/>
       <c r="AE21" s="4"/>
-      <c r="AF21" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="B2:AF21">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Z">
+  <conditionalFormatting sqref="B2:AE21">
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="Z">
       <formula>NOT(ISERROR(SEARCH("Z",B2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="U">
+    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="U">
       <formula>NOT(ISERROR(SEARCH("U",B2)))</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1367,7 +1532,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG13">
+  <conditionalFormatting sqref="AF13">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
